--- a/database/template-import-export/templates/template-st2023.xlsx
+++ b/database/template-import-export/templates/template-st2023.xlsx
@@ -24,7 +24,7 @@
     <t>Rumah tangga petani/ikan per desa (Sensus Pertanian 2023). Kolom ternak (JSON) tidak diedit via Excel.</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.34</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.44</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
